--- a/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 5(NE EV)_160kW.xlsx
+++ b/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 5(NE EV)_160kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,6 +3707,1062 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HMA_HK_01269</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HMA_HK_01270</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ADAS_D</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HMA_HK_01271</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HMA_HK_01272</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AFCU</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HMA_HK_01273</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HMA_HK_01274</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>APSM</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMA_HK_01275</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HMA_HK_01276</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HMA_HK_01277</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HMA_HK_01278</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HMA_HK_01279</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HMA_HK_01280</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HMA_HK_01281</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DSM-L</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HMA_HK_01282</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DSM-R</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HMA_HK_01283</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HMA_HK_01284</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HMA_HK_01285</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HMA_HK_01286</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HMA_HK_01287</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>HMA_HK_01288</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HMA_HK_01289</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HMA_HK_01290</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HMA_HK_01291</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HMA_HK_01292</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ICCU</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>HMA_HK_01293</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HMA_HK_01294</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MCU-F</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HMA_HK_01295</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MCU-R</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HMA_HK_01296</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HMA_HK_01297</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HMA_HK_01298</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HMA_HK_01299</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PCM</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HMA_HK_01300</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HMA_HK_01301</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PSM-RL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HMA_HK_01302</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PSM-RR</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HMA_HK_01303</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HMA_HK_01304</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HMA_HK_01305</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HMA_HK_01306</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HMA_HK_01307</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HMA_HK_01308</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HMA_HK_01309</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HMA_HK_01310</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HMA_HK_01311</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HMA_HK_01312</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VCMS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>HMA_HK_01313</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HMA_HK_00596</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HMA_HK_01315</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HMA_HK_01316</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
